--- a/corpus/C06.xlsx
+++ b/corpus/C06.xlsx
@@ -757,71 +757,71 @@
       </c>
       <c r="J5">
         <f>I9</f>
-        <v>7976.0</v>
+        <v>7785.0</v>
       </c>
       <c r="K5">
         <f>J9</f>
-        <v>8177.0</v>
+        <v>7981.0</v>
       </c>
       <c r="L5">
         <f>K9</f>
-        <v>8383.0</v>
+        <v>8182.0</v>
       </c>
       <c r="M5">
         <f>L9</f>
-        <v>8594.0</v>
+        <v>8389.0</v>
       </c>
       <c r="N5">
         <f>M9</f>
-        <v>8810.0</v>
+        <v>8600.0</v>
       </c>
       <c r="O5">
         <f>N9</f>
-        <v>9032.0</v>
+        <v>8817.0</v>
       </c>
       <c r="P5">
         <f>O9</f>
-        <v>9259.0</v>
+        <v>9039.0</v>
       </c>
       <c r="Q5">
         <f>P9</f>
-        <v>9492.0</v>
+        <v>9267.0</v>
       </c>
       <c r="R5">
         <f>Q9</f>
-        <v>9731.0</v>
+        <v>9501.0</v>
       </c>
       <c r="S5">
         <f>R9</f>
-        <v>9976.0</v>
+        <v>9741.0</v>
       </c>
       <c r="T5">
         <f>S9</f>
-        <v>10228.0</v>
+        <v>9986.0</v>
       </c>
       <c r="U5">
         <f>T9</f>
-        <v>10486.0</v>
+        <v>10237.0</v>
       </c>
       <c r="V5">
         <f>U9</f>
-        <v>10751.0</v>
+        <v>10495.0</v>
       </c>
       <c r="W5">
         <f>V9</f>
-        <v>11021.0</v>
+        <v>10759.0</v>
       </c>
       <c r="X5">
         <f>W9</f>
-        <v>11299.0</v>
+        <v>11030.0</v>
       </c>
       <c r="Y5">
         <f>X9</f>
-        <v>11584.0</v>
+        <v>11308.0</v>
       </c>
       <c r="Z5">
         <f>Y9</f>
-        <v>11876.0</v>
+        <v>11593.0</v>
       </c>
     </row>
     <row r="6">
@@ -860,71 +860,71 @@
       </c>
       <c r="J6">
         <f>ROUND(J5*Assumptions!$B$5,0)</f>
-        <v>419.0</v>
+        <v>409.0</v>
       </c>
       <c r="K6">
         <f>ROUND(K5*Assumptions!$B$5,0)</f>
-        <v>429.0</v>
+        <v>419.0</v>
       </c>
       <c r="L6">
         <f>ROUND(L5*Assumptions!$B$5,0)</f>
-        <v>440.0</v>
+        <v>430.0</v>
       </c>
       <c r="M6">
         <f>ROUND(M5*Assumptions!$B$5,0)</f>
-        <v>451.0</v>
+        <v>440.0</v>
       </c>
       <c r="N6">
         <f>ROUND(N5*Assumptions!$B$5,0)</f>
-        <v>463.0</v>
+        <v>452.0</v>
       </c>
       <c r="O6">
         <f>ROUND(O5*Assumptions!$B$5,0)</f>
-        <v>474.0</v>
+        <v>463.0</v>
       </c>
       <c r="P6">
         <f>ROUND(P5*Assumptions!$B$5,0)</f>
-        <v>486.0</v>
+        <v>475.0</v>
       </c>
       <c r="Q6">
         <f>ROUND(Q5*Assumptions!$B$5,0)</f>
-        <v>498.0</v>
+        <v>487.0</v>
       </c>
       <c r="R6">
         <f>ROUND(R5*Assumptions!$B$5,0)</f>
-        <v>511.0</v>
+        <v>499.0</v>
       </c>
       <c r="S6">
         <f>ROUND(S5*Assumptions!$B$5,0)</f>
-        <v>524.0</v>
+        <v>511.0</v>
       </c>
       <c r="T6">
         <f>ROUND(T5*Assumptions!$B$5,0)</f>
-        <v>537.0</v>
+        <v>524.0</v>
       </c>
       <c r="U6">
         <f>ROUND(U5*Assumptions!$B$5,0)</f>
-        <v>551.0</v>
+        <v>537.0</v>
       </c>
       <c r="V6">
         <f>ROUND(V5*Assumptions!$B$5,0)</f>
-        <v>564.0</v>
+        <v>551.0</v>
       </c>
       <c r="W6">
         <f>ROUND(W5*Assumptions!$B$5,0)</f>
-        <v>579.0</v>
+        <v>565.0</v>
       </c>
       <c r="X6">
         <f>ROUND(X5*Assumptions!$B$5,0)</f>
-        <v>593.0</v>
+        <v>579.0</v>
       </c>
       <c r="Y6">
         <f>ROUND(Y5*Assumptions!$B$5,0)</f>
-        <v>608.0</v>
+        <v>594.0</v>
       </c>
       <c r="Z6">
         <f>ROUND(Z5*Assumptions!$B$5,0)</f>
-        <v>623.0</v>
+        <v>609.0</v>
       </c>
     </row>
     <row r="7">
@@ -963,71 +963,71 @@
       </c>
       <c r="J7">
         <f>-ROUND(J5*Assumptions!$B$6,0)</f>
-        <v>-218.0</v>
+        <v>-213.0</v>
       </c>
       <c r="K7">
         <f>-ROUND(K5*Assumptions!$B$6,0)</f>
-        <v>-223.0</v>
+        <v>-218.0</v>
       </c>
       <c r="L7">
         <f>-ROUND(L5*Assumptions!$B$6,0)</f>
-        <v>-229.0</v>
+        <v>-223.0</v>
       </c>
       <c r="M7">
         <f>-ROUND(M5*Assumptions!$B$6,0)</f>
-        <v>-235.0</v>
+        <v>-229.0</v>
       </c>
       <c r="N7">
         <f>-ROUND(N5*Assumptions!$B$6,0)</f>
-        <v>-241.0</v>
+        <v>-235.0</v>
       </c>
       <c r="O7">
         <f>-ROUND(O5*Assumptions!$B$6,0)</f>
-        <v>-247.0</v>
+        <v>-241.0</v>
       </c>
       <c r="P7">
         <f>-ROUND(P5*Assumptions!$B$6,0)</f>
-        <v>-253.0</v>
+        <v>-247.0</v>
       </c>
       <c r="Q7">
         <f>-ROUND(Q5*Assumptions!$B$6,0)</f>
-        <v>-259.0</v>
+        <v>-253.0</v>
       </c>
       <c r="R7">
         <f>-ROUND(R5*Assumptions!$B$6,0)</f>
-        <v>-266.0</v>
+        <v>-259.0</v>
       </c>
       <c r="S7">
         <f>-ROUND(S5*Assumptions!$B$6,0)</f>
-        <v>-272.0</v>
+        <v>-266.0</v>
       </c>
       <c r="T7">
         <f>-ROUND(T5*Assumptions!$B$6,0)</f>
-        <v>-279.0</v>
+        <v>-273.0</v>
       </c>
       <c r="U7">
         <f>-ROUND(U5*Assumptions!$B$6,0)</f>
-        <v>-286.0</v>
+        <v>-279.0</v>
       </c>
       <c r="V7">
         <f>-ROUND(V5*Assumptions!$B$6,0)</f>
-        <v>-294.0</v>
+        <v>-287.0</v>
       </c>
       <c r="W7">
         <f>-ROUND(W5*Assumptions!$B$6,0)</f>
-        <v>-301.0</v>
+        <v>-294.0</v>
       </c>
       <c r="X7">
         <f>-ROUND(X5*Assumptions!$B$6,0)</f>
-        <v>-308.0</v>
+        <v>-301.0</v>
       </c>
       <c r="Y7">
         <f>-ROUND(Y5*Assumptions!$B$6,0)</f>
-        <v>-316.0</v>
+        <v>-309.0</v>
       </c>
       <c r="Z7">
         <f>-ROUND(Z5*Assumptions!$B$6,0)</f>
-        <v>-324.0</v>
+        <v>-316.0</v>
       </c>
     </row>
     <row r="9">
@@ -1061,76 +1061,76 @@
         <v>7780.0</v>
       </c>
       <c r="I9">
-        <f>I5+I6+I7</f>
-        <v>7976.0</v>
+        <f>H5+I6+I7</f>
+        <v>7785.0</v>
       </c>
       <c r="J9">
         <f>J5+J6+J7</f>
-        <v>8177.0</v>
+        <v>7981.0</v>
       </c>
       <c r="K9">
         <f>K5+K6+K7</f>
-        <v>8383.0</v>
+        <v>8182.0</v>
       </c>
       <c r="L9">
         <f>L5+L6+L7</f>
-        <v>8594.0</v>
+        <v>8389.0</v>
       </c>
       <c r="M9">
         <f>M5+M6+M7</f>
-        <v>8810.0</v>
+        <v>8600.0</v>
       </c>
       <c r="N9">
         <f>N5+N6+N7</f>
-        <v>9032.0</v>
+        <v>8817.0</v>
       </c>
       <c r="O9">
         <f>O5+O6+O7</f>
-        <v>9259.0</v>
+        <v>9039.0</v>
       </c>
       <c r="P9">
         <f>P5+P6+P7</f>
-        <v>9492.0</v>
+        <v>9267.0</v>
       </c>
       <c r="Q9">
         <f>Q5+Q6+Q7</f>
-        <v>9731.0</v>
+        <v>9501.0</v>
       </c>
       <c r="R9">
         <f>R5+R6+R7</f>
-        <v>9976.0</v>
+        <v>9741.0</v>
       </c>
       <c r="S9">
         <f>S5+S6+S7</f>
-        <v>10228.0</v>
+        <v>9986.0</v>
       </c>
       <c r="T9">
         <f>T5+T6+T7</f>
-        <v>10486.0</v>
+        <v>10237.0</v>
       </c>
       <c r="U9">
         <f>U5+U6+U7</f>
-        <v>10751.0</v>
+        <v>10495.0</v>
       </c>
       <c r="V9">
         <f>V5+V6+V7</f>
-        <v>11021.0</v>
+        <v>10759.0</v>
       </c>
       <c r="W9">
         <f>W5+W6+W7</f>
-        <v>11299.0</v>
+        <v>11030.0</v>
       </c>
       <c r="X9">
         <f>X5+X6+X7</f>
-        <v>11584.0</v>
+        <v>11308.0</v>
       </c>
       <c r="Y9">
         <f>Y5+Y6+Y7</f>
-        <v>11876.0</v>
+        <v>11593.0</v>
       </c>
       <c r="Z9">
         <f>Z5+Z6+Z7</f>
-        <v>12175.0</v>
+        <v>11886.0</v>
       </c>
     </row>
     <row r="11">
@@ -1268,75 +1268,75 @@
       </c>
       <c r="I13">
         <f>ROUND((I5+I9)/2,0)</f>
-        <v>7878.0</v>
+        <v>7783.0</v>
       </c>
       <c r="J13">
         <f>ROUND((J5+J9)/2,0)</f>
-        <v>8077.0</v>
+        <v>7883.0</v>
       </c>
       <c r="K13">
         <f>ROUND((K5+K9)/2,0)</f>
-        <v>8280.0</v>
+        <v>8082.0</v>
       </c>
       <c r="L13">
         <f>ROUND((L5+L9)/2,0)</f>
-        <v>8489.0</v>
+        <v>8286.0</v>
       </c>
       <c r="M13">
         <f>ROUND((M5+M9)/2,0)</f>
-        <v>8702.0</v>
+        <v>8495.0</v>
       </c>
       <c r="N13">
         <f>ROUND((N5+N9)/2,0)</f>
-        <v>8921.0</v>
+        <v>8709.0</v>
       </c>
       <c r="O13">
         <f>ROUND((O5+O9)/2,0)</f>
-        <v>9146.0</v>
+        <v>8928.0</v>
       </c>
       <c r="P13">
         <f>ROUND((P5+P9)/2,0)</f>
-        <v>9376.0</v>
+        <v>9153.0</v>
       </c>
       <c r="Q13">
         <f>ROUND((Q5+Q9)/2,0)</f>
-        <v>9612.0</v>
+        <v>9384.0</v>
       </c>
       <c r="R13">
         <f>ROUND((R5+R9)/2,0)</f>
-        <v>9854.0</v>
+        <v>9621.0</v>
       </c>
       <c r="S13">
         <f>ROUND((S5+S9)/2,0)</f>
-        <v>10102.0</v>
+        <v>9864.0</v>
       </c>
       <c r="T13">
         <f>ROUND((T5+T9)/2,0)</f>
-        <v>10357.0</v>
+        <v>10112.0</v>
       </c>
       <c r="U13">
         <f>ROUND((U5+U9)/2,0)</f>
-        <v>10619.0</v>
+        <v>10366.0</v>
       </c>
       <c r="V13">
         <f>ROUND((V5+V9)/2,0)</f>
-        <v>10886.0</v>
+        <v>10627.0</v>
       </c>
       <c r="W13">
         <f>ROUND((W5+W9)/2,0)</f>
-        <v>11160.0</v>
+        <v>10895.0</v>
       </c>
       <c r="X13">
         <f>ROUND((X5+X9)/2,0)</f>
-        <v>11442.0</v>
+        <v>11169.0</v>
       </c>
       <c r="Y13">
         <f>ROUND((Y5+Y9)/2,0)</f>
-        <v>11730.0</v>
+        <v>11451.0</v>
       </c>
       <c r="Z13">
         <f>ROUND((Z5+Z9)/2,0)</f>
-        <v>12026.0</v>
+        <v>11740.0</v>
       </c>
     </row>
     <row r="15">
@@ -1371,75 +1371,75 @@
       </c>
       <c r="I15">
         <f>ROUND(I13*I11,0)</f>
-        <v>745416.0</v>
+        <v>736427.0</v>
       </c>
       <c r="J15">
         <f>ROUND(J13*J11,0)</f>
-        <v>767719.0</v>
+        <v>749279.0</v>
       </c>
       <c r="K15">
         <f>ROUND(K13*K11,0)</f>
-        <v>790574.0</v>
+        <v>771669.0</v>
       </c>
       <c r="L15">
         <f>ROUND(L13*L11,0)</f>
-        <v>814180.0</v>
+        <v>794710.0</v>
       </c>
       <c r="M15">
         <f>ROUND(M13*M11,0)</f>
-        <v>838351.0</v>
+        <v>818408.0</v>
       </c>
       <c r="N15">
         <f>ROUND(N13*N11,0)</f>
-        <v>863285.0</v>
+        <v>842770.0</v>
       </c>
       <c r="O15">
         <f>ROUND(O13*O11,0)</f>
-        <v>889083.0</v>
+        <v>867891.0</v>
       </c>
       <c r="P15">
         <f>ROUND(P13*P11,0)</f>
-        <v>915566.0</v>
+        <v>893790.0</v>
       </c>
       <c r="Q15">
         <f>ROUND(Q13*Q11,0)</f>
-        <v>942841.0</v>
+        <v>920477.0</v>
       </c>
       <c r="R15">
         <f>ROUND(R13*R11,0)</f>
-        <v>970915.0</v>
+        <v>947957.0</v>
       </c>
       <c r="S15">
         <f>ROUND(S13*S11,0)</f>
-        <v>999795.0</v>
+        <v>976240.0</v>
       </c>
       <c r="T15">
         <f>ROUND(T13*T11,0)</f>
-        <v>1029693.0</v>
+        <v>1005335.0</v>
       </c>
       <c r="U15">
         <f>ROUND(U13*U11,0)</f>
-        <v>1060520.0</v>
+        <v>1035252.0</v>
       </c>
       <c r="V15">
         <f>ROUND(V13*V11,0)</f>
-        <v>1092084.0</v>
+        <v>1066101.0</v>
       </c>
       <c r="W15">
         <f>ROUND(W13*W11,0)</f>
-        <v>1124593.0</v>
+        <v>1097889.0</v>
       </c>
       <c r="X15">
         <f>ROUND(X13*X11,0)</f>
-        <v>1158159.0</v>
+        <v>1130526.0</v>
       </c>
       <c r="Y15">
         <f>ROUND(Y13*Y11,0)</f>
-        <v>1192706.0</v>
+        <v>1164338.0</v>
       </c>
       <c r="Z15">
         <f>ROUND(Z13*Z11,0)</f>
-        <v>1228336.0</v>
+        <v>1199124.0</v>
       </c>
     </row>
     <row r="17">
@@ -1474,75 +1474,75 @@
       </c>
       <c r="I17">
         <f>H17+I15</f>
-        <v>4786163.0</v>
+        <v>4777174.0</v>
       </c>
       <c r="J17">
         <f>I17+J15</f>
-        <v>5553882.0</v>
+        <v>5526453.0</v>
       </c>
       <c r="K17">
         <f>J17+K15</f>
-        <v>6344456.0</v>
+        <v>6298122.0</v>
       </c>
       <c r="L17">
         <f>K17+L15</f>
-        <v>7158636.0</v>
+        <v>7092832.0</v>
       </c>
       <c r="M17">
         <f>L17+M15</f>
-        <v>7996987.0</v>
+        <v>7911240.0</v>
       </c>
       <c r="N17">
         <f>M17+N15</f>
-        <v>8860272.0</v>
+        <v>8754010.0</v>
       </c>
       <c r="O17">
         <f>N17+O15</f>
-        <v>9749355.0</v>
+        <v>9621901.0</v>
       </c>
       <c r="P17">
         <f>O17+P15</f>
-        <v>10664921.0</v>
+        <v>10515691.0</v>
       </c>
       <c r="Q17">
         <f>P17+Q15</f>
-        <v>11607762.0</v>
+        <v>11436168.0</v>
       </c>
       <c r="R17">
         <f>Q17+R15</f>
-        <v>12578677.0</v>
+        <v>12384125.0</v>
       </c>
       <c r="S17">
         <f>R17+S15</f>
-        <v>13578472.0</v>
+        <v>13360365.0</v>
       </c>
       <c r="T17">
         <f>S17+T15</f>
-        <v>14608165.0</v>
+        <v>14365700.0</v>
       </c>
       <c r="U17">
         <f>T17+U15</f>
-        <v>15668685.0</v>
+        <v>15400952.0</v>
       </c>
       <c r="V17">
         <f>U17+V15</f>
-        <v>16760769.0</v>
+        <v>16467053.0</v>
       </c>
       <c r="W17">
         <f>V17+W15</f>
-        <v>17885362.0</v>
+        <v>17564942.0</v>
       </c>
       <c r="X17">
         <f>W17+X15</f>
-        <v>19043521.0</v>
+        <v>18695468.0</v>
       </c>
       <c r="Y17">
         <f>X17+Y15</f>
-        <v>20236227.0</v>
+        <v>19859806.0</v>
       </c>
       <c r="Z17">
         <f>Y17+Z15</f>
-        <v>21464563.0</v>
+        <v>21058930.0</v>
       </c>
     </row>
   </sheetData>
@@ -1676,100 +1676,100 @@
         </is>
       </c>
       <c r="C5">
-        <f>Assumptions!$B$12</f>
-        <v>21.0</v>
+        <f>Assumptions!$B$13</f>
+        <v>1.0</v>
       </c>
       <c r="D5">
         <f>C5+Assumptions!$B$13</f>
-        <v>22.0</v>
+        <v>2.0</v>
       </c>
       <c r="E5">
         <f>D5+Assumptions!$B$13</f>
-        <v>23.0</v>
+        <v>3.0</v>
       </c>
       <c r="F5">
         <f>E5+Assumptions!$B$13</f>
-        <v>24.0</v>
+        <v>4.0</v>
       </c>
       <c r="G5">
         <f>F5+Assumptions!$B$13</f>
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="H5">
         <f>G5+Assumptions!$B$13</f>
-        <v>26.0</v>
+        <v>6.0</v>
       </c>
       <c r="I5">
         <f>H5+Assumptions!$B$13</f>
-        <v>27.0</v>
+        <v>7.0</v>
       </c>
       <c r="J5">
         <f>I5+Assumptions!$B$13</f>
-        <v>28.0</v>
+        <v>8.0</v>
       </c>
       <c r="K5">
         <f>J5+Assumptions!$B$13</f>
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
       <c r="L5">
         <f>K5+Assumptions!$B$13</f>
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="M5">
         <f>L5+Assumptions!$B$13</f>
-        <v>31.0</v>
+        <v>11.0</v>
       </c>
       <c r="N5">
         <f>M5+Assumptions!$B$13</f>
-        <v>32.0</v>
+        <v>12.0</v>
       </c>
       <c r="O5">
         <f>N5+Assumptions!$B$13</f>
-        <v>33.0</v>
+        <v>13.0</v>
       </c>
       <c r="P5">
         <f>O5+Assumptions!$B$13</f>
-        <v>34.0</v>
+        <v>14.0</v>
       </c>
       <c r="Q5">
         <f>P5+Assumptions!$B$13</f>
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
       <c r="R5">
         <f>Q5+Assumptions!$B$13</f>
-        <v>36.0</v>
+        <v>16.0</v>
       </c>
       <c r="S5">
         <f>R5+Assumptions!$B$13</f>
-        <v>37.0</v>
+        <v>17.0</v>
       </c>
       <c r="T5">
         <f>S5+Assumptions!$B$13</f>
-        <v>38.0</v>
+        <v>18.0</v>
       </c>
       <c r="U5">
         <f>T5+Assumptions!$B$13</f>
-        <v>39.0</v>
+        <v>19.0</v>
       </c>
       <c r="V5">
         <f>U5+Assumptions!$B$13</f>
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="W5">
         <f>V5+Assumptions!$B$13</f>
-        <v>41.0</v>
+        <v>21.0</v>
       </c>
       <c r="X5">
         <f>W5+Assumptions!$B$13</f>
-        <v>42.0</v>
+        <v>22.0</v>
       </c>
       <c r="Y5">
         <f>X5+Assumptions!$B$13</f>
-        <v>43.0</v>
+        <v>23.0</v>
       </c>
       <c r="Z5">
         <f>Y5+Assumptions!$B$13</f>
-        <v>44.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="6">
@@ -1780,99 +1780,99 @@
       </c>
       <c r="C6">
         <f>ROUND(C5*Assumptions!$B$14/12,0)</f>
-        <v>146125.0</v>
+        <v>6958.0</v>
       </c>
       <c r="D6">
         <f>ROUND(D5*Assumptions!$B$14/12,0)</f>
-        <v>153083.0</v>
+        <v>13917.0</v>
       </c>
       <c r="E6">
         <f>ROUND(E5*Assumptions!$B$14/12,0)</f>
-        <v>160042.0</v>
+        <v>20875.0</v>
       </c>
       <c r="F6">
         <f>ROUND(F5*Assumptions!$B$14/12,0)</f>
-        <v>167000.0</v>
+        <v>27833.0</v>
       </c>
       <c r="G6">
         <f>ROUND(G5*Assumptions!$B$14/12,0)</f>
-        <v>173958.0</v>
+        <v>34792.0</v>
       </c>
       <c r="H6">
         <f>ROUND(H5*Assumptions!$B$14/12,0)</f>
-        <v>180917.0</v>
+        <v>41750.0</v>
       </c>
       <c r="I6">
         <f>ROUND(I5*Assumptions!$B$14/12,0)</f>
-        <v>187875.0</v>
+        <v>48708.0</v>
       </c>
       <c r="J6">
         <f>ROUND(J5*Assumptions!$B$14/12,0)</f>
-        <v>194833.0</v>
+        <v>55667.0</v>
       </c>
       <c r="K6">
         <f>ROUND(K5*Assumptions!$B$14/12,0)</f>
-        <v>201792.0</v>
+        <v>62625.0</v>
       </c>
       <c r="L6">
         <f>ROUND(L5*Assumptions!$B$14/12,0)</f>
-        <v>208750.0</v>
+        <v>69583.0</v>
       </c>
       <c r="M6">
         <f>ROUND(M5*Assumptions!$B$14/12,0)</f>
-        <v>215708.0</v>
+        <v>76542.0</v>
       </c>
       <c r="N6">
         <f>ROUND(N5*Assumptions!$B$14/12,0)</f>
-        <v>222667.0</v>
+        <v>83500.0</v>
       </c>
       <c r="O6">
         <f>ROUND(O5*Assumptions!$B$14/12,0)</f>
-        <v>229625.0</v>
+        <v>90458.0</v>
       </c>
       <c r="P6">
         <f>ROUND(P5*Assumptions!$B$14/12,0)</f>
-        <v>236583.0</v>
+        <v>97417.0</v>
       </c>
       <c r="Q6">
         <f>ROUND(Q5*Assumptions!$B$14/12,0)</f>
-        <v>243542.0</v>
+        <v>104375.0</v>
       </c>
       <c r="R6">
         <f>ROUND(R5*Assumptions!$B$14/12,0)</f>
-        <v>250500.0</v>
+        <v>111333.0</v>
       </c>
       <c r="S6">
         <f>ROUND(S5*Assumptions!$B$14/12,0)</f>
-        <v>257458.0</v>
+        <v>118292.0</v>
       </c>
       <c r="T6">
         <f>ROUND(T5*Assumptions!$B$14/12,0)</f>
-        <v>264417.0</v>
+        <v>125250.0</v>
       </c>
       <c r="U6">
         <f>ROUND(U5*Assumptions!$B$14/12,0)</f>
-        <v>271375.0</v>
+        <v>132208.0</v>
       </c>
       <c r="V6">
         <f>ROUND(V5*Assumptions!$B$14/12,0)</f>
-        <v>278333.0</v>
+        <v>139167.0</v>
       </c>
       <c r="W6">
         <f>ROUND(W5*Assumptions!$B$14/12,0)</f>
-        <v>285292.0</v>
+        <v>146125.0</v>
       </c>
       <c r="X6">
         <f>ROUND(X5*Assumptions!$B$14/12,0)</f>
-        <v>292250.0</v>
+        <v>153083.0</v>
       </c>
       <c r="Y6">
         <f>ROUND(Y5*Assumptions!$B$14/12,0)</f>
-        <v>299208.0</v>
+        <v>160042.0</v>
       </c>
       <c r="Z6">
         <f>ROUND(Z5*Assumptions!$B$14/12,0)</f>
-        <v>306167.0</v>
+        <v>167000.0</v>
       </c>
     </row>
     <row r="7">
@@ -1883,99 +1883,99 @@
       </c>
       <c r="C7">
         <f>ROUND(C6*Assumptions!$B$15,0)</f>
-        <v>17827.0</v>
+        <v>849.0</v>
       </c>
       <c r="D7">
         <f>ROUND(D6*Assumptions!$B$15,0)</f>
-        <v>18676.0</v>
+        <v>1698.0</v>
       </c>
       <c r="E7">
         <f>ROUND(E6*Assumptions!$B$15,0)</f>
-        <v>19525.0</v>
+        <v>2547.0</v>
       </c>
       <c r="F7">
         <f>ROUND(F6*Assumptions!$B$15,0)</f>
-        <v>20374.0</v>
+        <v>3396.0</v>
       </c>
       <c r="G7">
         <f>ROUND(G6*Assumptions!$B$15,0)</f>
-        <v>21223.0</v>
+        <v>4245.0</v>
       </c>
       <c r="H7">
         <f>ROUND(H6*Assumptions!$B$15,0)</f>
-        <v>22072.0</v>
+        <v>5094.0</v>
       </c>
       <c r="I7">
         <f>ROUND(I6*Assumptions!$B$15,0)</f>
-        <v>22921.0</v>
+        <v>5942.0</v>
       </c>
       <c r="J7">
         <f>ROUND(J6*Assumptions!$B$15,0)</f>
-        <v>23770.0</v>
+        <v>6791.0</v>
       </c>
       <c r="K7">
         <f>ROUND(K6*Assumptions!$B$15,0)</f>
-        <v>24619.0</v>
+        <v>7640.0</v>
       </c>
       <c r="L7">
         <f>ROUND(L6*Assumptions!$B$15,0)</f>
-        <v>25468.0</v>
+        <v>8489.0</v>
       </c>
       <c r="M7">
         <f>ROUND(M6*Assumptions!$B$15,0)</f>
-        <v>26316.0</v>
+        <v>9338.0</v>
       </c>
       <c r="N7">
         <f>ROUND(N6*Assumptions!$B$15,0)</f>
-        <v>27165.0</v>
+        <v>10187.0</v>
       </c>
       <c r="O7">
         <f>ROUND(O6*Assumptions!$B$15,0)</f>
-        <v>28014.0</v>
+        <v>11036.0</v>
       </c>
       <c r="P7">
         <f>ROUND(P6*Assumptions!$B$15,0)</f>
-        <v>28863.0</v>
+        <v>11885.0</v>
       </c>
       <c r="Q7">
         <f>ROUND(Q6*Assumptions!$B$15,0)</f>
-        <v>29712.0</v>
+        <v>12734.0</v>
       </c>
       <c r="R7">
         <f>ROUND(R6*Assumptions!$B$15,0)</f>
-        <v>30561.0</v>
+        <v>13583.0</v>
       </c>
       <c r="S7">
         <f>ROUND(S6*Assumptions!$B$15,0)</f>
-        <v>31410.0</v>
+        <v>14432.0</v>
       </c>
       <c r="T7">
         <f>ROUND(T6*Assumptions!$B$15,0)</f>
-        <v>32259.0</v>
+        <v>15281.0</v>
       </c>
       <c r="U7">
         <f>ROUND(U6*Assumptions!$B$15,0)</f>
-        <v>33108.0</v>
+        <v>16129.0</v>
       </c>
       <c r="V7">
         <f>ROUND(V6*Assumptions!$B$15,0)</f>
-        <v>33957.0</v>
+        <v>16978.0</v>
       </c>
       <c r="W7">
         <f>ROUND(W6*Assumptions!$B$15,0)</f>
-        <v>34806.0</v>
+        <v>17827.0</v>
       </c>
       <c r="X7">
         <f>ROUND(X6*Assumptions!$B$15,0)</f>
-        <v>35655.0</v>
+        <v>18676.0</v>
       </c>
       <c r="Y7">
         <f>ROUND(Y6*Assumptions!$B$15,0)</f>
-        <v>36503.0</v>
+        <v>19525.0</v>
       </c>
       <c r="Z7">
         <f>ROUND(Z6*Assumptions!$B$15,0)</f>
-        <v>37352.0</v>
+        <v>20374.0</v>
       </c>
     </row>
     <row r="8">
@@ -1986,99 +1986,99 @@
       </c>
       <c r="C8">
         <f>C6+C7</f>
-        <v>163952.0</v>
+        <v>7807.0</v>
       </c>
       <c r="D8">
         <f>D6+D7</f>
-        <v>171759.0</v>
+        <v>15615.0</v>
       </c>
       <c r="E8">
         <f>E6+E7</f>
-        <v>179567.0</v>
+        <v>23422.0</v>
       </c>
       <c r="F8">
         <f>F6+F7</f>
-        <v>187374.0</v>
+        <v>31229.0</v>
       </c>
       <c r="G8">
         <f>G6+G7</f>
-        <v>195181.0</v>
+        <v>39037.0</v>
       </c>
       <c r="H8">
         <f>H6+H7</f>
-        <v>202989.0</v>
+        <v>46844.0</v>
       </c>
       <c r="I8">
         <f>I6+I7</f>
-        <v>210796.0</v>
+        <v>54650.0</v>
       </c>
       <c r="J8">
         <f>J6+J7</f>
-        <v>218603.0</v>
+        <v>62458.0</v>
       </c>
       <c r="K8">
         <f>K6+K7</f>
-        <v>226411.0</v>
+        <v>70265.0</v>
       </c>
       <c r="L8">
         <f>L6+L7</f>
-        <v>234218.0</v>
+        <v>78072.0</v>
       </c>
       <c r="M8">
         <f>M6+M7</f>
-        <v>242024.0</v>
+        <v>85880.0</v>
       </c>
       <c r="N8">
         <f>N6+N7</f>
-        <v>249832.0</v>
+        <v>93687.0</v>
       </c>
       <c r="O8">
         <f>O6+O7</f>
-        <v>257639.0</v>
+        <v>101494.0</v>
       </c>
       <c r="P8">
         <f>P6+P7</f>
-        <v>265446.0</v>
+        <v>109302.0</v>
       </c>
       <c r="Q8">
         <f>Q6+Q7</f>
-        <v>273254.0</v>
+        <v>117109.0</v>
       </c>
       <c r="R8">
         <f>R6+R7</f>
-        <v>281061.0</v>
+        <v>124916.0</v>
       </c>
       <c r="S8">
         <f>S6+S7</f>
-        <v>288868.0</v>
+        <v>132724.0</v>
       </c>
       <c r="T8">
         <f>T6+T7</f>
-        <v>296676.0</v>
+        <v>140531.0</v>
       </c>
       <c r="U8">
         <f>U6+U7</f>
-        <v>304483.0</v>
+        <v>148337.0</v>
       </c>
       <c r="V8">
         <f>V6+V7</f>
-        <v>312290.0</v>
+        <v>156145.0</v>
       </c>
       <c r="W8">
         <f>W6+W7</f>
-        <v>320098.0</v>
+        <v>163952.0</v>
       </c>
       <c r="X8">
         <f>X6+X7</f>
-        <v>327905.0</v>
+        <v>171759.0</v>
       </c>
       <c r="Y8">
         <f>Y6+Y7</f>
-        <v>335711.0</v>
+        <v>179567.0</v>
       </c>
       <c r="Z8">
         <f>Z6+Z7</f>
-        <v>343519.0</v>
+        <v>187374.0</v>
       </c>
     </row>
     <row r="10">
@@ -2113,75 +2113,75 @@
       </c>
       <c r="I10">
         <f>ROUND(Revenue!I15*Assumptions!$B$11,0)</f>
-        <v>171818.0</v>
+        <v>169746.0</v>
       </c>
       <c r="J10">
         <f>ROUND(Revenue!J15*Assumptions!$B$11,0)</f>
-        <v>176959.0</v>
+        <v>172709.0</v>
       </c>
       <c r="K10">
         <f>ROUND(Revenue!K15*Assumptions!$B$11,0)</f>
-        <v>182227.0</v>
+        <v>177870.0</v>
       </c>
       <c r="L10">
         <f>ROUND(Revenue!L15*Assumptions!$B$11,0)</f>
-        <v>187668.0</v>
+        <v>183181.0</v>
       </c>
       <c r="M10">
         <f>ROUND(Revenue!M15*Assumptions!$B$11,0)</f>
-        <v>193240.0</v>
+        <v>188643.0</v>
       </c>
       <c r="N10">
         <f>ROUND(Revenue!N15*Assumptions!$B$11,0)</f>
-        <v>198987.0</v>
+        <v>194258.0</v>
       </c>
       <c r="O10">
         <f>ROUND(Revenue!O15*Assumptions!$B$11,0)</f>
-        <v>204934.0</v>
+        <v>200049.0</v>
       </c>
       <c r="P10">
         <f>ROUND(Revenue!P15*Assumptions!$B$11,0)</f>
-        <v>211038.0</v>
+        <v>206019.0</v>
       </c>
       <c r="Q10">
         <f>ROUND(Revenue!Q15*Assumptions!$B$11,0)</f>
-        <v>217325.0</v>
+        <v>212170.0</v>
       </c>
       <c r="R10">
         <f>ROUND(Revenue!R15*Assumptions!$B$11,0)</f>
-        <v>223796.0</v>
+        <v>218504.0</v>
       </c>
       <c r="S10">
         <f>ROUND(Revenue!S15*Assumptions!$B$11,0)</f>
-        <v>230453.0</v>
+        <v>225023.0</v>
       </c>
       <c r="T10">
         <f>ROUND(Revenue!T15*Assumptions!$B$11,0)</f>
-        <v>237344.0</v>
+        <v>231730.0</v>
       </c>
       <c r="U10">
         <f>ROUND(Revenue!U15*Assumptions!$B$11,0)</f>
-        <v>244450.0</v>
+        <v>238626.0</v>
       </c>
       <c r="V10">
         <f>ROUND(Revenue!V15*Assumptions!$B$11,0)</f>
-        <v>251725.0</v>
+        <v>245736.0</v>
       </c>
       <c r="W10">
         <f>ROUND(Revenue!W15*Assumptions!$B$11,0)</f>
-        <v>259219.0</v>
+        <v>253063.0</v>
       </c>
       <c r="X10">
         <f>ROUND(Revenue!X15*Assumptions!$B$11,0)</f>
-        <v>266956.0</v>
+        <v>260586.0</v>
       </c>
       <c r="Y10">
         <f>ROUND(Revenue!Y15*Assumptions!$B$11,0)</f>
-        <v>274919.0</v>
+        <v>268380.0</v>
       </c>
       <c r="Z10">
         <f>ROUND(Revenue!Z15*Assumptions!$B$11,0)</f>
-        <v>283131.0</v>
+        <v>276398.0</v>
       </c>
     </row>
     <row r="11">
@@ -2216,75 +2216,75 @@
       </c>
       <c r="I11">
         <f>ROUND(Revenue!I15*Assumptions!$B$16,0)</f>
-        <v>93773.0</v>
+        <v>92643.0</v>
       </c>
       <c r="J11">
         <f>ROUND(Revenue!J15*Assumptions!$B$16,0)</f>
-        <v>96579.0</v>
+        <v>94259.0</v>
       </c>
       <c r="K11">
         <f>ROUND(Revenue!K15*Assumptions!$B$16,0)</f>
-        <v>99454.0</v>
+        <v>97076.0</v>
       </c>
       <c r="L11">
         <f>ROUND(Revenue!L15*Assumptions!$B$16,0)</f>
-        <v>102424.0</v>
+        <v>99975.0</v>
       </c>
       <c r="M11">
         <f>ROUND(Revenue!M15*Assumptions!$B$16,0)</f>
-        <v>105465.0</v>
+        <v>102956.0</v>
       </c>
       <c r="N11">
         <f>ROUND(Revenue!N15*Assumptions!$B$16,0)</f>
-        <v>108601.0</v>
+        <v>106020.0</v>
       </c>
       <c r="O11">
         <f>ROUND(Revenue!O15*Assumptions!$B$16,0)</f>
-        <v>111847.0</v>
+        <v>109181.0</v>
       </c>
       <c r="P11">
         <f>ROUND(Revenue!P15*Assumptions!$B$16,0)</f>
-        <v>115178.0</v>
+        <v>112439.0</v>
       </c>
       <c r="Q11">
         <f>ROUND(Revenue!Q15*Assumptions!$B$16,0)</f>
-        <v>118609.0</v>
+        <v>115796.0</v>
       </c>
       <c r="R11">
         <f>ROUND(Revenue!R15*Assumptions!$B$16,0)</f>
-        <v>122141.0</v>
+        <v>119253.0</v>
       </c>
       <c r="S11">
         <f>ROUND(Revenue!S15*Assumptions!$B$16,0)</f>
-        <v>125774.0</v>
+        <v>122811.0</v>
       </c>
       <c r="T11">
         <f>ROUND(Revenue!T15*Assumptions!$B$16,0)</f>
-        <v>129535.0</v>
+        <v>126471.0</v>
       </c>
       <c r="U11">
         <f>ROUND(Revenue!U15*Assumptions!$B$16,0)</f>
-        <v>133413.0</v>
+        <v>130235.0</v>
       </c>
       <c r="V11">
         <f>ROUND(Revenue!V15*Assumptions!$B$16,0)</f>
-        <v>137384.0</v>
+        <v>134116.0</v>
       </c>
       <c r="W11">
         <f>ROUND(Revenue!W15*Assumptions!$B$16,0)</f>
-        <v>141474.0</v>
+        <v>138114.0</v>
       </c>
       <c r="X11">
         <f>ROUND(Revenue!X15*Assumptions!$B$16,0)</f>
-        <v>145696.0</v>
+        <v>142220.0</v>
       </c>
       <c r="Y11">
         <f>ROUND(Revenue!Y15*Assumptions!$B$16,0)</f>
-        <v>150042.0</v>
+        <v>146474.0</v>
       </c>
       <c r="Z11">
         <f>ROUND(Revenue!Z15*Assumptions!$B$16,0)</f>
-        <v>154525.0</v>
+        <v>150850.0</v>
       </c>
     </row>
     <row r="12">
@@ -2398,99 +2398,99 @@
       </c>
       <c r="C14">
         <f>C8+C10+C11+C12</f>
-        <v>420128.0</v>
+        <v>263983.0</v>
       </c>
       <c r="D14">
         <f>D8+D10+D11+D12</f>
-        <v>434697.0</v>
+        <v>278553.0</v>
       </c>
       <c r="E14">
         <f>E8+E10+E11+E12</f>
-        <v>449476.0</v>
+        <v>293331.0</v>
       </c>
       <c r="F14">
         <f>F8+F10+F11+F12</f>
-        <v>464472.0</v>
+        <v>308327.0</v>
       </c>
       <c r="G14">
         <f>G8+G10+G11+G12</f>
-        <v>479691.0</v>
+        <v>323547.0</v>
       </c>
       <c r="H14">
         <f>H8+H10+H11+H12</f>
-        <v>495100.0</v>
+        <v>338955.0</v>
       </c>
       <c r="I14">
         <f>I8+I10+I11+I12</f>
-        <v>510700.0</v>
+        <v>351352.0</v>
       </c>
       <c r="J14">
         <f>J8+J10+J11+J12</f>
-        <v>526591.0</v>
+        <v>363876.0</v>
       </c>
       <c r="K14">
         <f>K8+K10+K11+K12</f>
-        <v>542680.0</v>
+        <v>379799.0</v>
       </c>
       <c r="L14">
         <f>L8+L10+L11+L12</f>
-        <v>559036.0</v>
+        <v>395954.0</v>
       </c>
       <c r="M14">
         <f>M8+M10+M11+M12</f>
-        <v>575594.0</v>
+        <v>412344.0</v>
       </c>
       <c r="N14">
         <f>N8+N10+N11+N12</f>
-        <v>592424.0</v>
+        <v>428969.0</v>
       </c>
       <c r="O14">
         <f>O8+O10+O11+O12</f>
-        <v>609564.0</v>
+        <v>445868.0</v>
       </c>
       <c r="P14">
         <f>P8+P10+P11+P12</f>
-        <v>626947.0</v>
+        <v>463045.0</v>
       </c>
       <c r="Q14">
         <f>Q8+Q10+Q11+Q12</f>
-        <v>644614.0</v>
+        <v>480501.0</v>
       </c>
       <c r="R14">
         <f>R8+R10+R11+R12</f>
-        <v>662566.0</v>
+        <v>498241.0</v>
       </c>
       <c r="S14">
         <f>S8+S10+S11+S12</f>
-        <v>680805.0</v>
+        <v>516268.0</v>
       </c>
       <c r="T14">
         <f>T8+T10+T11+T12</f>
-        <v>699408.0</v>
+        <v>534585.0</v>
       </c>
       <c r="U14">
         <f>U8+U10+U11+U12</f>
-        <v>718342.0</v>
+        <v>553194.0</v>
       </c>
       <c r="V14">
         <f>V8+V10+V11+V12</f>
-        <v>737539.0</v>
+        <v>572137.0</v>
       </c>
       <c r="W14">
         <f>W8+W10+W11+W12</f>
-        <v>757076.0</v>
+        <v>591414.0</v>
       </c>
       <c r="X14">
         <f>X8+X10+X11+X12</f>
-        <v>776987.0</v>
+        <v>610995.0</v>
       </c>
       <c r="Y14">
         <f>Y8+Y10+Y11+Y12</f>
-        <v>797248.0</v>
+        <v>630997.0</v>
       </c>
       <c r="Z14">
         <f>Z8+Z10+Z11+Z12</f>
-        <v>817897.0</v>
+        <v>651344.0</v>
       </c>
     </row>
   </sheetData>
@@ -2654,79 +2654,79 @@
       </c>
       <c r="I5">
         <f>Revenue!I15</f>
-        <v>745416.0</v>
+        <v>736427.0</v>
       </c>
       <c r="J5">
         <f>Revenue!J15</f>
-        <v>767719.0</v>
+        <v>749279.0</v>
       </c>
       <c r="K5">
         <f>Revenue!K15</f>
-        <v>790574.0</v>
+        <v>771669.0</v>
       </c>
       <c r="L5">
         <f>Revenue!L15</f>
-        <v>814180.0</v>
+        <v>794710.0</v>
       </c>
       <c r="M5">
         <f>Revenue!M15</f>
-        <v>838351.0</v>
+        <v>818408.0</v>
       </c>
       <c r="N5">
         <f>Revenue!N15</f>
-        <v>863285.0</v>
+        <v>842770.0</v>
       </c>
       <c r="O5">
         <f>Revenue!O15</f>
-        <v>889083.0</v>
+        <v>867891.0</v>
       </c>
       <c r="P5">
         <f>Revenue!P15</f>
-        <v>915566.0</v>
+        <v>893790.0</v>
       </c>
       <c r="Q5">
         <f>Revenue!Q15</f>
-        <v>942841.0</v>
+        <v>920477.0</v>
       </c>
       <c r="R5">
         <f>Revenue!R15</f>
-        <v>970915.0</v>
+        <v>947957.0</v>
       </c>
       <c r="S5">
         <f>Revenue!S15</f>
-        <v>999795.0</v>
+        <v>976240.0</v>
       </c>
       <c r="T5">
         <f>Revenue!T15</f>
-        <v>1029693.0</v>
+        <v>1005335.0</v>
       </c>
       <c r="U5">
         <f>Revenue!U15</f>
-        <v>1060520.0</v>
+        <v>1035252.0</v>
       </c>
       <c r="V5">
         <f>Revenue!V15</f>
-        <v>1092084.0</v>
+        <v>1066101.0</v>
       </c>
       <c r="W5">
         <f>Revenue!W15</f>
-        <v>1124593.0</v>
+        <v>1097889.0</v>
       </c>
       <c r="X5">
         <f>Revenue!X15</f>
-        <v>1158159.0</v>
+        <v>1130526.0</v>
       </c>
       <c r="Y5">
         <f>Revenue!Y15</f>
-        <v>1192706.0</v>
+        <v>1164338.0</v>
       </c>
       <c r="Z5">
         <f>Revenue!Z15</f>
-        <v>1228336.0</v>
+        <v>1199124.0</v>
       </c>
       <c r="AA5">
         <f>SUM(C5:Z5)</f>
-        <v>21464563.0</v>
+        <v>21058930.0</v>
       </c>
     </row>
     <row r="6">
@@ -2761,79 +2761,79 @@
       </c>
       <c r="I6">
         <f>-Costs!I10</f>
-        <v>-171818.0</v>
+        <v>-169746.0</v>
       </c>
       <c r="J6">
         <f>-Costs!J10</f>
-        <v>-176959.0</v>
+        <v>-172709.0</v>
       </c>
       <c r="K6">
         <f>-Costs!K10</f>
-        <v>-182227.0</v>
+        <v>-177870.0</v>
       </c>
       <c r="L6">
         <f>-Costs!L10</f>
-        <v>-187668.0</v>
+        <v>-183181.0</v>
       </c>
       <c r="M6">
         <f>-Costs!M10</f>
-        <v>-193240.0</v>
+        <v>-188643.0</v>
       </c>
       <c r="N6">
         <f>-Costs!N10</f>
-        <v>-198987.0</v>
+        <v>-194258.0</v>
       </c>
       <c r="O6">
         <f>-Costs!O10</f>
-        <v>-204934.0</v>
+        <v>-200049.0</v>
       </c>
       <c r="P6">
         <f>-Costs!P10</f>
-        <v>-211038.0</v>
+        <v>-206019.0</v>
       </c>
       <c r="Q6">
         <f>-Costs!Q10</f>
-        <v>-217325.0</v>
+        <v>-212170.0</v>
       </c>
       <c r="R6">
         <f>-Costs!R10</f>
-        <v>-223796.0</v>
+        <v>-218504.0</v>
       </c>
       <c r="S6">
         <f>-Costs!S10</f>
-        <v>-230453.0</v>
+        <v>-225023.0</v>
       </c>
       <c r="T6">
         <f>-Costs!T10</f>
-        <v>-237344.0</v>
+        <v>-231730.0</v>
       </c>
       <c r="U6">
         <f>-Costs!U10</f>
-        <v>-244450.0</v>
+        <v>-238626.0</v>
       </c>
       <c r="V6">
         <f>-Costs!V10</f>
-        <v>-251725.0</v>
+        <v>-245736.0</v>
       </c>
       <c r="W6">
         <f>-Costs!W10</f>
-        <v>-259219.0</v>
+        <v>-253063.0</v>
       </c>
       <c r="X6">
         <f>-Costs!X10</f>
-        <v>-266956.0</v>
+        <v>-260586.0</v>
       </c>
       <c r="Y6">
         <f>-Costs!Y10</f>
-        <v>-274919.0</v>
+        <v>-268380.0</v>
       </c>
       <c r="Z6">
         <f>-Costs!Z10</f>
-        <v>-283131.0</v>
+        <v>-276398.0</v>
       </c>
       <c r="AA6">
         <f>SUM(C6:Z6)</f>
-        <v>-4947582.0</v>
+        <v>-4854084.0</v>
       </c>
     </row>
     <row r="7">
@@ -2868,79 +2868,79 @@
       </c>
       <c r="I7">
         <f>I5+I6</f>
-        <v>573598.0</v>
+        <v>566681.0</v>
       </c>
       <c r="J7">
         <f>J5+J6</f>
-        <v>590760.0</v>
+        <v>576570.0</v>
       </c>
       <c r="K7">
-        <f>K5+K6</f>
-        <v>608347.0</v>
+        <f>K5-K6</f>
+        <v>949539.0</v>
       </c>
       <c r="L7">
         <f>L5+L6</f>
-        <v>626512.0</v>
+        <v>611529.0</v>
       </c>
       <c r="M7">
         <f>M5+M6</f>
-        <v>645111.0</v>
+        <v>629765.0</v>
       </c>
       <c r="N7">
         <f>N5+N6</f>
-        <v>664298.0</v>
+        <v>648512.0</v>
       </c>
       <c r="O7">
         <f>O5+O6</f>
-        <v>684149.0</v>
+        <v>667842.0</v>
       </c>
       <c r="P7">
         <f>P5+P6</f>
-        <v>704528.0</v>
+        <v>687771.0</v>
       </c>
       <c r="Q7">
         <f>Q5+Q6</f>
-        <v>725516.0</v>
+        <v>708307.0</v>
       </c>
       <c r="R7">
         <f>R5+R6</f>
-        <v>747119.0</v>
+        <v>729453.0</v>
       </c>
       <c r="S7">
         <f>S5+S6</f>
-        <v>769342.0</v>
+        <v>751217.0</v>
       </c>
       <c r="T7">
         <f>T5+T6</f>
-        <v>792349.0</v>
+        <v>773605.0</v>
       </c>
       <c r="U7">
         <f>U5+U6</f>
-        <v>816070.0</v>
+        <v>796626.0</v>
       </c>
       <c r="V7">
         <f>V5+V6</f>
-        <v>840359.0</v>
+        <v>820365.0</v>
       </c>
       <c r="W7">
         <f>W5+W6</f>
-        <v>865374.0</v>
+        <v>844826.0</v>
       </c>
       <c r="X7">
         <f>X5+X6</f>
-        <v>891203.0</v>
+        <v>869940.0</v>
       </c>
       <c r="Y7">
         <f>Y5+Y6</f>
-        <v>917787.0</v>
+        <v>895958.0</v>
       </c>
       <c r="Z7">
         <f>Z5+Z6</f>
-        <v>945205.0</v>
+        <v>922726.0</v>
       </c>
       <c r="AA7">
         <f>SUM(C7:Z7)</f>
-        <v>16516981.0</v>
+        <v>16560586.0</v>
       </c>
     </row>
     <row r="8">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="K8">
         <f>IF(K5=0,0,ROUND(K7/K5,4))</f>
-        <v>0.7695</v>
+        <v>1.2305</v>
       </c>
       <c r="L8">
         <f>IF(L5=0,0,ROUND(L7/L5,4))</f>
@@ -3054,103 +3054,103 @@
       </c>
       <c r="C10">
         <f>-Costs!C8</f>
-        <v>-163952.0</v>
+        <v>-7807.0</v>
       </c>
       <c r="D10">
         <f>-Costs!D8</f>
-        <v>-171759.0</v>
+        <v>-15615.0</v>
       </c>
       <c r="E10">
         <f>-Costs!E8</f>
-        <v>-179567.0</v>
+        <v>-23422.0</v>
       </c>
       <c r="F10">
         <f>-Costs!F8</f>
-        <v>-187374.0</v>
+        <v>-31229.0</v>
       </c>
       <c r="G10">
         <f>-Costs!G8</f>
-        <v>-195181.0</v>
+        <v>-39037.0</v>
       </c>
       <c r="H10">
         <f>-Costs!H8</f>
-        <v>-202989.0</v>
+        <v>-46844.0</v>
       </c>
       <c r="I10">
         <f>-Costs!I8</f>
-        <v>-210796.0</v>
+        <v>-54650.0</v>
       </c>
       <c r="J10">
         <f>-Costs!J8</f>
-        <v>-218603.0</v>
+        <v>-62458.0</v>
       </c>
       <c r="K10">
         <f>-Costs!K8</f>
-        <v>-226411.0</v>
+        <v>-70265.0</v>
       </c>
       <c r="L10">
         <f>-Costs!L8</f>
-        <v>-234218.0</v>
+        <v>-78072.0</v>
       </c>
       <c r="M10">
         <f>-Costs!M8</f>
-        <v>-242024.0</v>
+        <v>-85880.0</v>
       </c>
       <c r="N10">
         <f>-Costs!N8</f>
-        <v>-249832.0</v>
+        <v>-93687.0</v>
       </c>
       <c r="O10">
         <f>-Costs!O8</f>
-        <v>-257639.0</v>
+        <v>-101494.0</v>
       </c>
       <c r="P10">
         <f>-Costs!P8</f>
-        <v>-265446.0</v>
+        <v>-109302.0</v>
       </c>
       <c r="Q10">
         <f>-Costs!Q8</f>
-        <v>-273254.0</v>
+        <v>-117109.0</v>
       </c>
       <c r="R10">
         <f>-Costs!R8</f>
-        <v>-281061.0</v>
+        <v>-124916.0</v>
       </c>
       <c r="S10">
         <f>-Costs!S8</f>
-        <v>-288868.0</v>
+        <v>-132724.0</v>
       </c>
       <c r="T10">
         <f>-Costs!T8</f>
-        <v>-296676.0</v>
+        <v>-140531.0</v>
       </c>
       <c r="U10">
         <f>-Costs!U8</f>
-        <v>-304483.0</v>
+        <v>-148337.0</v>
       </c>
       <c r="V10">
         <f>-Costs!V8</f>
-        <v>-312290.0</v>
+        <v>-156145.0</v>
       </c>
       <c r="W10">
         <f>-Costs!W8</f>
-        <v>-320098.0</v>
+        <v>-163952.0</v>
       </c>
       <c r="X10">
         <f>-Costs!X8</f>
-        <v>-327905.0</v>
+        <v>-171759.0</v>
       </c>
       <c r="Y10">
         <f>-Costs!Y8</f>
-        <v>-335711.0</v>
+        <v>-179567.0</v>
       </c>
       <c r="Z10">
         <f>-Costs!Z8</f>
-        <v>-343519.0</v>
+        <v>-187374.0</v>
       </c>
       <c r="AA10">
         <f>SUM(C10:Z10)</f>
-        <v>-6089656.0</v>
+        <v>-2342176.0</v>
       </c>
     </row>
     <row r="11">
@@ -3185,79 +3185,79 @@
       </c>
       <c r="I11">
         <f>-Costs!I11</f>
-        <v>-93773.0</v>
+        <v>-92643.0</v>
       </c>
       <c r="J11">
         <f>-Costs!J11</f>
-        <v>-96579.0</v>
+        <v>-94259.0</v>
       </c>
       <c r="K11">
         <f>-Costs!K11</f>
-        <v>-99454.0</v>
+        <v>-97076.0</v>
       </c>
       <c r="L11">
         <f>-Costs!L11</f>
-        <v>-102424.0</v>
+        <v>-99975.0</v>
       </c>
       <c r="M11">
         <f>-Costs!M11</f>
-        <v>-105465.0</v>
+        <v>-102956.0</v>
       </c>
       <c r="N11">
         <f>-Costs!N11</f>
-        <v>-108601.0</v>
+        <v>-106020.0</v>
       </c>
       <c r="O11">
         <f>-Costs!O11</f>
-        <v>-111847.0</v>
+        <v>-109181.0</v>
       </c>
       <c r="P11">
         <f>-Costs!P11</f>
-        <v>-115178.0</v>
+        <v>-112439.0</v>
       </c>
       <c r="Q11">
         <f>-Costs!Q11</f>
-        <v>-118609.0</v>
+        <v>-115796.0</v>
       </c>
       <c r="R11">
         <f>-Costs!R11</f>
-        <v>-122141.0</v>
+        <v>-119253.0</v>
       </c>
       <c r="S11">
         <f>-Costs!S11</f>
-        <v>-125774.0</v>
+        <v>-122811.0</v>
       </c>
       <c r="T11">
         <f>-Costs!T11</f>
-        <v>-129535.0</v>
+        <v>-126471.0</v>
       </c>
       <c r="U11">
         <f>-Costs!U11</f>
-        <v>-133413.0</v>
+        <v>-130235.0</v>
       </c>
       <c r="V11">
         <f>-Costs!V11</f>
-        <v>-137384.0</v>
+        <v>-134116.0</v>
       </c>
       <c r="W11">
         <f>-Costs!W11</f>
-        <v>-141474.0</v>
+        <v>-138114.0</v>
       </c>
       <c r="X11">
         <f>-Costs!X11</f>
-        <v>-145696.0</v>
+        <v>-142220.0</v>
       </c>
       <c r="Y11">
         <f>-Costs!Y11</f>
-        <v>-150042.0</v>
+        <v>-146474.0</v>
       </c>
       <c r="Z11">
         <f>-Costs!Z11</f>
-        <v>-154525.0</v>
+        <v>-150850.0</v>
       </c>
       <c r="AA11">
         <f>SUM(C11:Z11)</f>
-        <v>-2700240.0</v>
+        <v>-2649215.0</v>
       </c>
     </row>
     <row r="12">
@@ -3375,103 +3375,103 @@
       </c>
       <c r="C13">
         <f>C10+C11+C12</f>
-        <v>-276073.0</v>
+        <v>-119928.0</v>
       </c>
       <c r="D13">
         <f>D10+D11+D12</f>
-        <v>-286354.0</v>
+        <v>-130210.0</v>
       </c>
       <c r="E13">
         <f>E10+E11+E12</f>
-        <v>-296711.0</v>
+        <v>-140566.0</v>
       </c>
       <c r="F13">
         <f>F10+F11+F12</f>
-        <v>-307143.0</v>
+        <v>-150998.0</v>
       </c>
       <c r="G13">
         <f>G10+G11+G12</f>
-        <v>-317655.0</v>
+        <v>-161511.0</v>
       </c>
       <c r="H13">
         <f>H10+H11+H12</f>
-        <v>-328235.0</v>
+        <v>-172090.0</v>
       </c>
       <c r="I13">
         <f>I10+I11+I12</f>
-        <v>-338882.0</v>
+        <v>-181606.0</v>
       </c>
       <c r="J13">
         <f>J10+J11+J12</f>
-        <v>-349632.0</v>
+        <v>-191167.0</v>
       </c>
       <c r="K13">
         <f>K10+K11+K12</f>
-        <v>-360453.0</v>
+        <v>-201929.0</v>
       </c>
       <c r="L13">
         <f>L10+L11+L12</f>
-        <v>-371368.0</v>
+        <v>-212773.0</v>
       </c>
       <c r="M13">
         <f>M10+M11+M12</f>
-        <v>-382354.0</v>
+        <v>-223701.0</v>
       </c>
       <c r="N13">
         <f>N10+N11+N12</f>
-        <v>-393437.0</v>
+        <v>-234711.0</v>
       </c>
       <c r="O13">
         <f>O10+O11+O12</f>
-        <v>-404630.0</v>
+        <v>-245819.0</v>
       </c>
       <c r="P13">
         <f>P10+P11+P12</f>
-        <v>-415909.0</v>
+        <v>-257026.0</v>
       </c>
       <c r="Q13">
         <f>Q10+Q11+Q12</f>
-        <v>-427289.0</v>
+        <v>-268331.0</v>
       </c>
       <c r="R13">
         <f>R10+R11+R12</f>
-        <v>-438770.0</v>
+        <v>-279737.0</v>
       </c>
       <c r="S13">
         <f>S10+S11+S12</f>
-        <v>-450352.0</v>
+        <v>-291245.0</v>
       </c>
       <c r="T13">
         <f>T10+T11+T12</f>
-        <v>-462064.0</v>
+        <v>-302855.0</v>
       </c>
       <c r="U13">
         <f>U10+U11+U12</f>
-        <v>-473892.0</v>
+        <v>-314568.0</v>
       </c>
       <c r="V13">
         <f>V10+V11+V12</f>
-        <v>-485814.0</v>
+        <v>-326401.0</v>
       </c>
       <c r="W13">
         <f>W10+W11+W12</f>
-        <v>-497857.0</v>
+        <v>-338351.0</v>
       </c>
       <c r="X13">
         <f>X10+X11+X12</f>
-        <v>-510031.0</v>
+        <v>-350409.0</v>
       </c>
       <c r="Y13">
         <f>Y10+Y11+Y12</f>
-        <v>-522329.0</v>
+        <v>-362617.0</v>
       </c>
       <c r="Z13">
         <f>Z10+Z11+Z12</f>
-        <v>-534766.0</v>
+        <v>-374946.0</v>
       </c>
       <c r="AA13">
         <f>SUM(C13:Z13)</f>
-        <v>-9632000.0</v>
+        <v>-5833495.0</v>
       </c>
     </row>
     <row r="15">
@@ -3482,103 +3482,103 @@
       </c>
       <c r="C15">
         <f>C7+C13</f>
-        <v>204838.0</v>
+        <v>360983.0</v>
       </c>
       <c r="D15">
         <f>D7+D13</f>
-        <v>208872.0</v>
+        <v>365016.0</v>
       </c>
       <c r="E15">
         <f>E7+E13</f>
-        <v>213279.0</v>
+        <v>369424.0</v>
       </c>
       <c r="F15">
         <f>F7+F13</f>
-        <v>218083.0</v>
+        <v>374228.0</v>
       </c>
       <c r="G15">
         <f>G7+G13</f>
-        <v>223284.0</v>
+        <v>379428.0</v>
       </c>
       <c r="H15">
         <f>H7+H13</f>
-        <v>228827.0</v>
+        <v>384972.0</v>
       </c>
       <c r="I15">
         <f>I7+I13</f>
-        <v>234716.0</v>
+        <v>385075.0</v>
       </c>
       <c r="J15">
         <f>J7+J13</f>
-        <v>241128.0</v>
+        <v>385403.0</v>
       </c>
       <c r="K15">
         <f>K7+K13</f>
-        <v>247894.0</v>
+        <v>747610.0</v>
       </c>
       <c r="L15">
         <f>L7+L13</f>
-        <v>255144.0</v>
+        <v>398756.0</v>
       </c>
       <c r="M15">
         <f>M7+M13</f>
-        <v>262757.0</v>
+        <v>406064.0</v>
       </c>
       <c r="N15">
         <f>N7+N13</f>
-        <v>270861.0</v>
+        <v>413801.0</v>
       </c>
       <c r="O15">
         <f>O7+O13</f>
-        <v>279519.0</v>
+        <v>422023.0</v>
       </c>
       <c r="P15">
         <f>P7+P13</f>
-        <v>288619.0</v>
+        <v>430745.0</v>
       </c>
       <c r="Q15">
         <f>Q7+Q13</f>
-        <v>298227.0</v>
+        <v>439976.0</v>
       </c>
       <c r="R15">
         <f>R7+R13</f>
-        <v>308349.0</v>
+        <v>449716.0</v>
       </c>
       <c r="S15">
         <f>S7+S13</f>
-        <v>318990.0</v>
+        <v>459972.0</v>
       </c>
       <c r="T15">
         <f>T7+T13</f>
-        <v>330285.0</v>
+        <v>470750.0</v>
       </c>
       <c r="U15">
         <f>U7+U13</f>
-        <v>342178.0</v>
+        <v>482058.0</v>
       </c>
       <c r="V15">
         <f>V7+V13</f>
-        <v>354545.0</v>
+        <v>493964.0</v>
       </c>
       <c r="W15">
         <f>W7+W13</f>
-        <v>367517.0</v>
+        <v>506475.0</v>
       </c>
       <c r="X15">
         <f>X7+X13</f>
-        <v>381172.0</v>
+        <v>519531.0</v>
       </c>
       <c r="Y15">
         <f>Y7+Y13</f>
-        <v>395458.0</v>
+        <v>533341.0</v>
       </c>
       <c r="Z15">
         <f>Z7+Z13</f>
-        <v>410439.0</v>
+        <v>547780.0</v>
       </c>
       <c r="AA15">
         <f>SUM(C15:Z15)</f>
-        <v>6884981.0</v>
+        <v>10727091.0</v>
       </c>
     </row>
     <row r="16">
@@ -3589,99 +3589,99 @@
       </c>
       <c r="C16">
         <f>IF(C5=0,0,ROUND(C15/C5,4))</f>
-        <v>0.3278</v>
+        <v>0.5776</v>
       </c>
       <c r="D16">
         <f>IF(D5=0,0,ROUND(D15/D5,4))</f>
-        <v>0.3246</v>
+        <v>0.5672</v>
       </c>
       <c r="E16">
         <f>IF(E5=0,0,ROUND(E15/E5,4))</f>
-        <v>0.3218</v>
+        <v>0.5574</v>
       </c>
       <c r="F16">
         <f>IF(F5=0,0,ROUND(F15/F5,4))</f>
-        <v>0.3195</v>
+        <v>0.5483</v>
       </c>
       <c r="G16">
         <f>IF(G5=0,0,ROUND(G15/G5,4))</f>
-        <v>0.3176</v>
+        <v>0.5397</v>
       </c>
       <c r="H16">
         <f>IF(H5=0,0,ROUND(H15/H5,4))</f>
-        <v>0.3161</v>
+        <v>0.5318</v>
       </c>
       <c r="I16">
         <f>IF(I5=0,0,ROUND(I15/I5,4))</f>
-        <v>0.3149</v>
+        <v>0.5229</v>
       </c>
       <c r="J16">
         <f>IF(J5=0,0,ROUND(J15/J5,4))</f>
-        <v>0.3141</v>
+        <v>0.5144</v>
       </c>
       <c r="K16">
         <f>IF(K5=0,0,ROUND(K15/K5,4))</f>
-        <v>0.3136</v>
+        <v>0.9688</v>
       </c>
       <c r="L16">
         <f>IF(L5=0,0,ROUND(L15/L5,4))</f>
-        <v>0.3134</v>
+        <v>0.5018</v>
       </c>
       <c r="M16">
         <f>IF(M5=0,0,ROUND(M15/M5,4))</f>
-        <v>0.3134</v>
+        <v>0.4962</v>
       </c>
       <c r="N16">
         <f>IF(N5=0,0,ROUND(N15/N5,4))</f>
-        <v>0.3138</v>
+        <v>0.491</v>
       </c>
       <c r="O16">
         <f>IF(O5=0,0,ROUND(O15/O5,4))</f>
-        <v>0.3144</v>
+        <v>0.4863</v>
       </c>
       <c r="P16">
         <f>IF(P5=0,0,ROUND(P15/P5,4))</f>
-        <v>0.3152</v>
+        <v>0.4819</v>
       </c>
       <c r="Q16">
         <f>IF(Q5=0,0,ROUND(Q15/Q5,4))</f>
-        <v>0.3163</v>
+        <v>0.478</v>
       </c>
       <c r="R16">
         <f>IF(R5=0,0,ROUND(R15/R5,4))</f>
-        <v>0.3176</v>
+        <v>0.4744</v>
       </c>
       <c r="S16">
         <f>IF(S5=0,0,ROUND(S15/S5,4))</f>
-        <v>0.3191</v>
+        <v>0.4712</v>
       </c>
       <c r="T16">
         <f>IF(T5=0,0,ROUND(T15/T5,4))</f>
-        <v>0.3208</v>
+        <v>0.4683</v>
       </c>
       <c r="U16">
         <f>IF(U5=0,0,ROUND(U15/U5,4))</f>
-        <v>0.3227</v>
+        <v>0.4656</v>
       </c>
       <c r="V16">
         <f>IF(V5=0,0,ROUND(V15/V5,4))</f>
-        <v>0.3246</v>
+        <v>0.4633</v>
       </c>
       <c r="W16">
         <f>IF(W5=0,0,ROUND(W15/W5,4))</f>
-        <v>0.3268</v>
+        <v>0.4613</v>
       </c>
       <c r="X16">
         <f>IF(X5=0,0,ROUND(X15/X5,4))</f>
-        <v>0.3291</v>
+        <v>0.4595</v>
       </c>
       <c r="Y16">
         <f>IF(Y5=0,0,ROUND(Y15/Y5,4))</f>
-        <v>0.3316</v>
+        <v>0.4581</v>
       </c>
       <c r="Z16">
         <f>IF(Z5=0,0,ROUND(Z15/Z5,4))</f>
-        <v>0.3341</v>
+        <v>0.4568</v>
       </c>
     </row>
     <row r="18">
@@ -3692,99 +3692,99 @@
       </c>
       <c r="C18">
         <f>C15</f>
-        <v>204838.0</v>
+        <v>360983.0</v>
       </c>
       <c r="D18">
         <f>C18+D15</f>
-        <v>413710.0</v>
+        <v>725999.0</v>
       </c>
       <c r="E18">
         <f>D18+E15</f>
-        <v>626989.0</v>
+        <v>1095423.0</v>
       </c>
       <c r="F18">
         <f>E18+F15</f>
-        <v>845072.0</v>
+        <v>1469651.0</v>
       </c>
       <c r="G18">
         <f>F18+G15</f>
-        <v>1068356.0</v>
+        <v>1849079.0</v>
       </c>
       <c r="H18">
         <f>G18+H15</f>
-        <v>1297183.0</v>
+        <v>2234051.0</v>
       </c>
       <c r="I18">
         <f>H18+I15</f>
-        <v>1531899.0</v>
+        <v>2619126.0</v>
       </c>
       <c r="J18">
         <f>I18+J15</f>
-        <v>1773027.0</v>
+        <v>3004529.0</v>
       </c>
       <c r="K18">
         <f>J18+K15</f>
-        <v>2020921.0</v>
+        <v>3752139.0</v>
       </c>
       <c r="L18">
         <f>K18+L15</f>
-        <v>2276065.0</v>
+        <v>4150895.0</v>
       </c>
       <c r="M18">
         <f>L18+M15</f>
-        <v>2538822.0</v>
+        <v>4556959.0</v>
       </c>
       <c r="N18">
         <f>M18+N15</f>
-        <v>2809683.0</v>
+        <v>4970760.0</v>
       </c>
       <c r="O18">
         <f>N18+O15</f>
-        <v>3089202.0</v>
+        <v>5392783.0</v>
       </c>
       <c r="P18">
         <f>O18+P15</f>
-        <v>3377821.0</v>
+        <v>5823528.0</v>
       </c>
       <c r="Q18">
         <f>P18+Q15</f>
-        <v>3676048.0</v>
+        <v>6263504.0</v>
       </c>
       <c r="R18">
         <f>Q18+R15</f>
-        <v>3984397.0</v>
+        <v>6713220.0</v>
       </c>
       <c r="S18">
         <f>R18+S15</f>
-        <v>4303387.0</v>
+        <v>7173192.0</v>
       </c>
       <c r="T18">
         <f>S18+T15</f>
-        <v>4633672.0</v>
+        <v>7643942.0</v>
       </c>
       <c r="U18">
         <f>T18+U15</f>
-        <v>4975850.0</v>
+        <v>8126000.0</v>
       </c>
       <c r="V18">
         <f>U18+V15</f>
-        <v>5330395.0</v>
+        <v>8619964.0</v>
       </c>
       <c r="W18">
         <f>V18+W15</f>
-        <v>5697912.0</v>
+        <v>9126439.0</v>
       </c>
       <c r="X18">
         <f>W18+X15</f>
-        <v>6079084.0</v>
+        <v>9645970.0</v>
       </c>
       <c r="Y18">
         <f>X18+Y15</f>
-        <v>6474542.0</v>
+        <v>10179311.0</v>
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>6884981.0</v>
+        <v>10727091.0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B3">
         <f>Revenue!Z17</f>
-        <v>21464563.0</v>
+        <v>21058930.0</v>
       </c>
     </row>
     <row r="4">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>6884981.0</v>
+        <v>10727091.0</v>
       </c>
     </row>
     <row r="5">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B5">
         <f>SUM('P&amp;L'!O15:Z15)</f>
-        <v>4075298.0</v>
+        <v>5756331.0</v>
       </c>
     </row>
     <row r="6">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B7">
         <f>ROUND(B5*B6,0)</f>
-        <v>33824973.0</v>
+        <v>47777547.0</v>
       </c>
     </row>
     <row r="8">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>31474973.0</v>
+        <v>45427547.0</v>
       </c>
     </row>
     <row r="11">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>286874.2083333333</v>
+        <v>446962.125</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B12">
         <f>MAX('P&amp;L'!C15:Z15)</f>
-        <v>410439.0</v>
+        <v>747610.0</v>
       </c>
     </row>
     <row r="13">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="B13">
         <f>MIN('P&amp;L'!C15:Z15)</f>
-        <v>204838.0</v>
+        <v>360983.0</v>
       </c>
     </row>
     <row r="14">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>6884981.0</v>
+        <v>10727091.0</v>
       </c>
     </row>
     <row r="15">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B15">
         <f>ABS(B12-B13)</f>
-        <v>205601.0</v>
+        <v>386627.0</v>
       </c>
     </row>
   </sheetData>
